--- a/SWTest/Outputs/Finalists/Railblazer_Analysis_Final.xlsx
+++ b/SWTest/Outputs/Finalists/Railblazer_Analysis_Final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\Outputs\Finalists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EB064B-1268-4814-B7E6-F6800F502850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F10BC70-72E5-4F6D-9248-FF68909BF0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3570" yWindow="7710" windowWidth="14190" windowHeight="8460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1444,7 +1444,7 @@
     <col min="5" max="5" width="8.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="66.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="82.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="45.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -5070,7 +5070,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>342</v>
       </c>

--- a/SWTest/Outputs/Finalists/Railblazer_Analysis_Final.xlsx
+++ b/SWTest/Outputs/Finalists/Railblazer_Analysis_Final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\Outputs\Finalists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93FF5998-5EED-49B0-ADA3-202F0151D87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AAFBC0-5339-4F79-83E4-A94192274AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="12972" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18780" yWindow="3312" windowWidth="16416" windowHeight="8856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,9 +43,6 @@
     <t>Dependency</t>
   </si>
   <si>
-    <t>Access Level (Wintrac)</t>
-  </si>
-  <si>
     <t>Unit of Measurement</t>
   </si>
   <si>
@@ -1065,6 +1062,9 @@
   </si>
   <si>
     <t>Engine Break-In Request</t>
+  </si>
+  <si>
+    <t>Access Level (WinTrac)</t>
   </si>
 </sst>
 </file>
@@ -1431,26 +1431,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O116"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="111.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="57.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="67.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="111.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="67.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="175" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1473,4563 +1473,4563 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O6" t="s">
         <v>33</v>
       </c>
-      <c r="K6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" t="s">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>35</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>36</v>
       </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J7" s="2">
         <v>33</v>
       </c>
       <c r="K7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>39</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>41</v>
       </c>
-      <c r="K8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" t="s">
-        <v>19</v>
-      </c>
-      <c r="M8" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>42</v>
       </c>
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N9" t="s">
+        <v>44</v>
+      </c>
+      <c r="O9" t="s">
         <v>45</v>
       </c>
-      <c r="O9" t="s">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>47</v>
       </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" t="s">
         <v>49</v>
       </c>
-      <c r="K10" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" t="s">
-        <v>19</v>
-      </c>
-      <c r="N10" t="s">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>51</v>
       </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J11" s="2">
         <v>3</v>
       </c>
       <c r="K11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
         <v>53</v>
       </c>
-      <c r="B12" t="s">
-        <v>54</v>
-      </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J12" s="2">
         <v>4</v>
       </c>
       <c r="K12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
         <v>55</v>
       </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J13" s="2">
         <v>203</v>
       </c>
       <c r="K13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
         <v>57</v>
       </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J14" s="2">
         <v>204</v>
       </c>
       <c r="K14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
         <v>59</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" t="s">
-        <v>49</v>
-      </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>61</v>
       </c>
-      <c r="K15" t="s">
-        <v>19</v>
-      </c>
-      <c r="L15" t="s">
-        <v>19</v>
-      </c>
-      <c r="M15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>62</v>
       </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J16" s="2">
         <v>5</v>
       </c>
       <c r="K16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
         <v>64</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>66</v>
       </c>
-      <c r="K17" t="s">
-        <v>19</v>
-      </c>
-      <c r="L17" t="s">
-        <v>19</v>
-      </c>
-      <c r="M17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>67</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>69</v>
       </c>
-      <c r="K18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L18" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>70</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K19" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>71</v>
       </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K19" t="s">
-        <v>19</v>
-      </c>
-      <c r="L19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>72</v>
       </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>75</v>
       </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L21" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" t="s">
         <v>77</v>
       </c>
-      <c r="K21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L21" t="s">
-        <v>19</v>
-      </c>
-      <c r="M21" t="s">
-        <v>19</v>
-      </c>
-      <c r="N21" t="s">
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>79</v>
       </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K22" t="s">
+        <v>19</v>
+      </c>
+      <c r="L22" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" t="s">
         <v>81</v>
       </c>
-      <c r="K22" t="s">
-        <v>20</v>
-      </c>
-      <c r="L22" t="s">
-        <v>19</v>
-      </c>
-      <c r="M22" t="s">
-        <v>19</v>
-      </c>
-      <c r="N22" t="s">
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>83</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="2" t="s">
+      <c r="K23" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" t="s">
+        <v>18</v>
+      </c>
+      <c r="M23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>85</v>
       </c>
-      <c r="K23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>86</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" t="s">
+        <v>48</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" t="s">
-        <v>49</v>
-      </c>
-      <c r="J24" s="2" t="s">
+      <c r="K24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" t="s">
+        <v>18</v>
+      </c>
+      <c r="M24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>88</v>
       </c>
-      <c r="K24" t="s">
-        <v>19</v>
-      </c>
-      <c r="L24" t="s">
-        <v>19</v>
-      </c>
-      <c r="M24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>89</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C25" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="2" t="s">
+      <c r="K25" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" t="s">
+        <v>18</v>
+      </c>
+      <c r="O25" t="s">
         <v>91</v>
       </c>
-      <c r="K25" t="s">
-        <v>19</v>
-      </c>
-      <c r="L25" t="s">
-        <v>19</v>
-      </c>
-      <c r="M25" t="s">
-        <v>19</v>
-      </c>
-      <c r="O25" t="s">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>93</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C26" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" t="s">
-        <v>21</v>
-      </c>
-      <c r="H26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="2" t="s">
+      <c r="K26" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" t="s">
+        <v>18</v>
+      </c>
+      <c r="M26" t="s">
+        <v>18</v>
+      </c>
+      <c r="O26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>95</v>
       </c>
-      <c r="K26" t="s">
-        <v>19</v>
-      </c>
-      <c r="L26" t="s">
-        <v>19</v>
-      </c>
-      <c r="M26" t="s">
-        <v>19</v>
-      </c>
-      <c r="O26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>96</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" t="s">
-        <v>21</v>
-      </c>
-      <c r="H27" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="2" t="s">
+      <c r="K27" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>98</v>
       </c>
-      <c r="K27" t="s">
-        <v>19</v>
-      </c>
-      <c r="L27" t="s">
-        <v>19</v>
-      </c>
-      <c r="M27" t="s">
-        <v>19</v>
-      </c>
-      <c r="O27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>99</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" t="s">
         <v>100</v>
-      </c>
-      <c r="C28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" t="s">
-        <v>19</v>
-      </c>
-      <c r="G28" t="s">
-        <v>21</v>
-      </c>
-      <c r="H28" t="s">
-        <v>101</v>
       </c>
       <c r="J28" s="2">
         <v>89</v>
       </c>
       <c r="K28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>103</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C29" t="s">
+      <c r="K29" t="s">
+        <v>18</v>
+      </c>
+      <c r="L29" t="s">
+        <v>18</v>
+      </c>
+      <c r="M29" t="s">
+        <v>18</v>
+      </c>
+      <c r="O29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C30" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
         <v>31</v>
       </c>
-      <c r="D29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" t="s">
-        <v>32</v>
-      </c>
-      <c r="H29" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K29" t="s">
-        <v>19</v>
-      </c>
-      <c r="L29" t="s">
-        <v>19</v>
-      </c>
-      <c r="M29" t="s">
-        <v>19</v>
-      </c>
-      <c r="O29" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>107</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="H30" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L30" t="s">
+        <v>18</v>
+      </c>
+      <c r="M30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>108</v>
       </c>
-      <c r="C30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" t="s">
-        <v>32</v>
-      </c>
-      <c r="H30" t="s">
-        <v>22</v>
-      </c>
-      <c r="K30" t="s">
-        <v>19</v>
-      </c>
-      <c r="L30" t="s">
-        <v>19</v>
-      </c>
-      <c r="M30" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>109</v>
       </c>
-      <c r="B31" t="s">
-        <v>110</v>
-      </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D31" t="b">
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N31" t="s">
+        <v>110</v>
+      </c>
+      <c r="O31" t="s">
         <v>111</v>
       </c>
-      <c r="O31" t="s">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>113</v>
       </c>
-      <c r="B32" t="s">
-        <v>114</v>
-      </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D32" t="b">
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N32" t="s">
+        <v>110</v>
+      </c>
+      <c r="O32" t="s">
         <v>111</v>
       </c>
-      <c r="O32" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" t="s">
         <v>115</v>
       </c>
-      <c r="B33" t="s">
-        <v>116</v>
-      </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D33" t="b">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
+        <v>110</v>
+      </c>
+      <c r="O33" t="s">
         <v>111</v>
       </c>
-      <c r="O33" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" t="s">
         <v>117</v>
       </c>
-      <c r="B34" t="s">
-        <v>118</v>
-      </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D34" t="b">
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N34" t="s">
+        <v>110</v>
+      </c>
+      <c r="O34" t="s">
         <v>111</v>
       </c>
-      <c r="O34" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" t="s">
         <v>119</v>
       </c>
-      <c r="B35" t="s">
-        <v>120</v>
-      </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D35" t="b">
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N35" t="s">
+        <v>110</v>
+      </c>
+      <c r="O35" t="s">
         <v>111</v>
       </c>
-      <c r="O35" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" t="s">
         <v>121</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" t="s">
+        <v>48</v>
+      </c>
+      <c r="J36" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C36" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" t="s">
-        <v>49</v>
-      </c>
-      <c r="J36" s="2" t="s">
+      <c r="K36" t="s">
+        <v>18</v>
+      </c>
+      <c r="L36" t="s">
+        <v>18</v>
+      </c>
+      <c r="M36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>123</v>
       </c>
-      <c r="K36" t="s">
-        <v>19</v>
-      </c>
-      <c r="L36" t="s">
-        <v>19</v>
-      </c>
-      <c r="M36" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>124</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" t="s">
+        <v>48</v>
+      </c>
+      <c r="K37" t="s">
+        <v>18</v>
+      </c>
+      <c r="L37" t="s">
+        <v>18</v>
+      </c>
+      <c r="M37" t="s">
+        <v>18</v>
+      </c>
+      <c r="O37" t="s">
         <v>125</v>
       </c>
-      <c r="C37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" t="s">
-        <v>20</v>
-      </c>
-      <c r="F37" t="s">
-        <v>19</v>
-      </c>
-      <c r="G37" t="s">
-        <v>21</v>
-      </c>
-      <c r="H37" t="s">
-        <v>49</v>
-      </c>
-      <c r="K37" t="s">
-        <v>19</v>
-      </c>
-      <c r="L37" t="s">
-        <v>19</v>
-      </c>
-      <c r="M37" t="s">
-        <v>19</v>
-      </c>
-      <c r="O37" t="s">
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>127</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C38" t="s">
-        <v>31</v>
-      </c>
-      <c r="D38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" t="s">
-        <v>19</v>
-      </c>
-      <c r="G38" t="s">
-        <v>21</v>
-      </c>
-      <c r="H38" t="s">
-        <v>22</v>
-      </c>
-      <c r="J38" s="2" t="s">
+      <c r="K38" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" t="s">
+        <v>18</v>
+      </c>
+      <c r="M38" t="s">
+        <v>18</v>
+      </c>
+      <c r="O38" t="s">
         <v>129</v>
       </c>
-      <c r="K38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L38" t="s">
-        <v>19</v>
-      </c>
-      <c r="M38" t="s">
-        <v>19</v>
-      </c>
-      <c r="O38" t="s">
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>131</v>
       </c>
-      <c r="B39" t="s">
-        <v>132</v>
-      </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D39" t="b">
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N39" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>134</v>
       </c>
-      <c r="B40" t="s">
-        <v>135</v>
-      </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D40" t="b">
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N40" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>137</v>
       </c>
-      <c r="B41" t="s">
-        <v>138</v>
-      </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D41" t="b">
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J41" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K41" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" t="s">
+        <v>18</v>
+      </c>
+      <c r="M41" t="s">
+        <v>18</v>
+      </c>
+      <c r="N41" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>139</v>
       </c>
-      <c r="K41" t="s">
-        <v>19</v>
-      </c>
-      <c r="L41" t="s">
-        <v>19</v>
-      </c>
-      <c r="M41" t="s">
-        <v>19</v>
-      </c>
-      <c r="N41" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>140</v>
       </c>
-      <c r="B42" t="s">
-        <v>141</v>
-      </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D42" t="b">
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N42" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" t="s">
         <v>142</v>
       </c>
-      <c r="B43" t="s">
-        <v>143</v>
-      </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D43" t="b">
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N43" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" t="s">
         <v>144</v>
       </c>
-      <c r="B44" t="s">
-        <v>145</v>
-      </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D44" t="b">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N44" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" t="s">
         <v>146</v>
       </c>
-      <c r="B45" t="s">
-        <v>147</v>
-      </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D45" t="b">
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N45" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" t="s">
         <v>148</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K46" t="s">
+        <v>18</v>
+      </c>
+      <c r="L46" t="s">
+        <v>18</v>
+      </c>
+      <c r="M46" t="s">
+        <v>18</v>
+      </c>
+      <c r="O46" t="s">
         <v>149</v>
       </c>
-      <c r="C46" t="s">
-        <v>31</v>
-      </c>
-      <c r="D46" t="s">
-        <v>20</v>
-      </c>
-      <c r="E46" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" t="s">
-        <v>19</v>
-      </c>
-      <c r="G46" t="s">
-        <v>21</v>
-      </c>
-      <c r="H46" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K46" t="s">
-        <v>19</v>
-      </c>
-      <c r="L46" t="s">
-        <v>19</v>
-      </c>
-      <c r="M46" t="s">
-        <v>19</v>
-      </c>
-      <c r="O46" t="s">
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>151</v>
       </c>
-      <c r="B47" t="s">
-        <v>152</v>
-      </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D47" t="b">
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N47" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>154</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K48" t="s">
+        <v>18</v>
+      </c>
+      <c r="L48" t="s">
+        <v>18</v>
+      </c>
+      <c r="M48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>155</v>
       </c>
-      <c r="C48" t="s">
-        <v>31</v>
-      </c>
-      <c r="D48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G48" t="s">
-        <v>21</v>
-      </c>
-      <c r="H48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K48" t="s">
-        <v>19</v>
-      </c>
-      <c r="L48" t="s">
-        <v>19</v>
-      </c>
-      <c r="M48" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>156</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K49" t="s">
+        <v>18</v>
+      </c>
+      <c r="L49" t="s">
+        <v>18</v>
+      </c>
+      <c r="M49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>157</v>
       </c>
-      <c r="C49" t="s">
-        <v>31</v>
-      </c>
-      <c r="D49" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" t="s">
-        <v>19</v>
-      </c>
-      <c r="G49" t="s">
-        <v>21</v>
-      </c>
-      <c r="H49" t="s">
-        <v>22</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K49" t="s">
-        <v>19</v>
-      </c>
-      <c r="L49" t="s">
-        <v>19</v>
-      </c>
-      <c r="M49" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="B50" t="s">
         <v>158</v>
       </c>
-      <c r="B50" t="s">
-        <v>159</v>
-      </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D50" t="b">
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J50" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="K50" t="s">
+        <v>19</v>
+      </c>
+      <c r="L50" t="s">
+        <v>18</v>
+      </c>
+      <c r="M50" t="s">
+        <v>18</v>
+      </c>
+      <c r="N50" t="s">
         <v>160</v>
       </c>
-      <c r="K50" t="s">
-        <v>20</v>
-      </c>
-      <c r="L50" t="s">
-        <v>19</v>
-      </c>
-      <c r="M50" t="s">
-        <v>19</v>
-      </c>
-      <c r="N50" t="s">
+      <c r="O50" t="s">
         <v>161</v>
       </c>
-      <c r="O50" t="s">
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>163</v>
       </c>
-      <c r="B51" t="s">
-        <v>164</v>
-      </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D51" t="b">
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J51" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K51" t="s">
+        <v>18</v>
+      </c>
+      <c r="L51" t="s">
+        <v>18</v>
+      </c>
+      <c r="M51" t="s">
+        <v>18</v>
+      </c>
+      <c r="O51" t="s">
         <v>165</v>
       </c>
-      <c r="K51" t="s">
-        <v>19</v>
-      </c>
-      <c r="L51" t="s">
-        <v>19</v>
-      </c>
-      <c r="M51" t="s">
-        <v>19</v>
-      </c>
-      <c r="O51" t="s">
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>167</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
+        <v>43</v>
+      </c>
+      <c r="D52" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" t="s">
+        <v>48</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K52" t="s">
+        <v>18</v>
+      </c>
+      <c r="L52" t="s">
+        <v>18</v>
+      </c>
+      <c r="M52" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>168</v>
       </c>
-      <c r="C52" t="s">
-        <v>44</v>
-      </c>
-      <c r="D52" t="s">
-        <v>20</v>
-      </c>
-      <c r="E52" t="s">
-        <v>19</v>
-      </c>
-      <c r="F52" t="s">
-        <v>19</v>
-      </c>
-      <c r="G52" t="s">
-        <v>21</v>
-      </c>
-      <c r="H52" t="s">
-        <v>49</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="K52" t="s">
-        <v>19</v>
-      </c>
-      <c r="L52" t="s">
-        <v>19</v>
-      </c>
-      <c r="M52" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
         <v>169</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D53" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" t="s">
+        <v>100</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K53" t="s">
+        <v>18</v>
+      </c>
+      <c r="L53" t="s">
+        <v>18</v>
+      </c>
+      <c r="M53" t="s">
+        <v>18</v>
+      </c>
+      <c r="N53" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>170</v>
       </c>
-      <c r="C53" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" t="s">
-        <v>19</v>
-      </c>
-      <c r="G53" t="s">
-        <v>21</v>
-      </c>
-      <c r="H53" t="s">
-        <v>101</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="K53" t="s">
-        <v>19</v>
-      </c>
-      <c r="L53" t="s">
-        <v>19</v>
-      </c>
-      <c r="M53" t="s">
-        <v>19</v>
-      </c>
-      <c r="N53" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>171</v>
       </c>
-      <c r="B54" t="s">
-        <v>172</v>
-      </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D54" t="b">
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N54" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
         <v>174</v>
       </c>
-      <c r="B55" t="s">
-        <v>175</v>
-      </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D55" t="b">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N55" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
         <v>177</v>
       </c>
-      <c r="B56" t="s">
-        <v>178</v>
-      </c>
       <c r="C56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D56" t="b">
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J56" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="K56" t="s">
+        <v>18</v>
+      </c>
+      <c r="L56" t="s">
+        <v>18</v>
+      </c>
+      <c r="M56" t="s">
+        <v>19</v>
+      </c>
+      <c r="N56" t="s">
         <v>179</v>
       </c>
-      <c r="K56" t="s">
-        <v>19</v>
-      </c>
-      <c r="L56" t="s">
-        <v>19</v>
-      </c>
-      <c r="M56" t="s">
-        <v>20</v>
-      </c>
-      <c r="N56" t="s">
+      <c r="O56" t="s">
         <v>180</v>
       </c>
-      <c r="O56" t="s">
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>182</v>
       </c>
-      <c r="B57" t="s">
-        <v>183</v>
-      </c>
       <c r="C57" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D57" t="b">
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J57" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K57" t="s">
+        <v>18</v>
+      </c>
+      <c r="L57" t="s">
+        <v>18</v>
+      </c>
+      <c r="M57" t="s">
+        <v>19</v>
+      </c>
+      <c r="N57" t="s">
+        <v>179</v>
+      </c>
+      <c r="O57" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>184</v>
       </c>
-      <c r="K57" t="s">
-        <v>19</v>
-      </c>
-      <c r="L57" t="s">
-        <v>19</v>
-      </c>
-      <c r="M57" t="s">
-        <v>20</v>
-      </c>
-      <c r="N57" t="s">
-        <v>180</v>
-      </c>
-      <c r="O57" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
         <v>185</v>
       </c>
-      <c r="B58" t="s">
-        <v>186</v>
-      </c>
       <c r="C58" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D58" t="b">
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J58" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K58" t="s">
+        <v>18</v>
+      </c>
+      <c r="L58" t="s">
+        <v>18</v>
+      </c>
+      <c r="M58" t="s">
+        <v>19</v>
+      </c>
+      <c r="N58" t="s">
+        <v>179</v>
+      </c>
+      <c r="O58" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>187</v>
       </c>
-      <c r="K58" t="s">
-        <v>19</v>
-      </c>
-      <c r="L58" t="s">
-        <v>19</v>
-      </c>
-      <c r="M58" t="s">
-        <v>20</v>
-      </c>
-      <c r="N58" t="s">
-        <v>180</v>
-      </c>
-      <c r="O58" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="B59" t="s">
         <v>188</v>
       </c>
-      <c r="B59" t="s">
-        <v>189</v>
-      </c>
       <c r="C59" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D59" t="b">
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H59" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M59" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" t="s">
         <v>190</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
+        <v>43</v>
+      </c>
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>20</v>
+      </c>
+      <c r="H60" t="s">
+        <v>100</v>
+      </c>
+      <c r="K60" t="s">
+        <v>18</v>
+      </c>
+      <c r="L60" t="s">
+        <v>18</v>
+      </c>
+      <c r="M60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>191</v>
       </c>
-      <c r="C60" t="s">
-        <v>44</v>
-      </c>
-      <c r="D60" t="s">
-        <v>20</v>
-      </c>
-      <c r="E60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F60" t="s">
-        <v>19</v>
-      </c>
-      <c r="G60" t="s">
-        <v>21</v>
-      </c>
-      <c r="H60" t="s">
-        <v>101</v>
-      </c>
-      <c r="K60" t="s">
-        <v>19</v>
-      </c>
-      <c r="L60" t="s">
-        <v>19</v>
-      </c>
-      <c r="M60" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>192</v>
       </c>
-      <c r="B61" t="s">
-        <v>193</v>
-      </c>
       <c r="C61" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D61" t="b">
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H61" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N61" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
         <v>195</v>
       </c>
-      <c r="B62" t="s">
-        <v>196</v>
-      </c>
       <c r="C62" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D62" t="b">
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H62" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J62" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="K62" t="s">
+        <v>19</v>
+      </c>
+      <c r="L62" t="s">
+        <v>18</v>
+      </c>
+      <c r="M62" t="s">
+        <v>18</v>
+      </c>
+      <c r="N62" t="s">
+        <v>193</v>
+      </c>
+      <c r="O62" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>197</v>
       </c>
-      <c r="K62" t="s">
-        <v>20</v>
-      </c>
-      <c r="L62" t="s">
-        <v>19</v>
-      </c>
-      <c r="M62" t="s">
-        <v>19</v>
-      </c>
-      <c r="N62" t="s">
-        <v>194</v>
-      </c>
-      <c r="O62" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>198</v>
       </c>
-      <c r="B63" t="s">
-        <v>199</v>
-      </c>
       <c r="C63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D63" t="b">
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J63" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="K63" t="s">
+        <v>19</v>
+      </c>
+      <c r="L63" t="s">
+        <v>18</v>
+      </c>
+      <c r="M63" t="s">
+        <v>18</v>
+      </c>
+      <c r="N63" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>200</v>
       </c>
-      <c r="K63" t="s">
-        <v>20</v>
-      </c>
-      <c r="L63" t="s">
-        <v>19</v>
-      </c>
-      <c r="M63" t="s">
-        <v>19</v>
-      </c>
-      <c r="N63" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>201</v>
       </c>
-      <c r="B64" t="s">
-        <v>202</v>
-      </c>
       <c r="C64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D64" t="b">
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N64" t="s">
+        <v>202</v>
+      </c>
+      <c r="O64" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>203</v>
       </c>
-      <c r="O64" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
         <v>204</v>
       </c>
-      <c r="B65" t="s">
-        <v>205</v>
-      </c>
       <c r="C65" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J65" s="2">
         <v>66</v>
       </c>
       <c r="K65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N65" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>205</v>
+      </c>
+      <c r="B66" t="s">
         <v>206</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
+        <v>43</v>
+      </c>
+      <c r="D66" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
         <v>207</v>
       </c>
-      <c r="C66" t="s">
-        <v>44</v>
-      </c>
-      <c r="D66" t="s">
-        <v>20</v>
-      </c>
-      <c r="E66" t="s">
-        <v>19</v>
-      </c>
-      <c r="F66" t="s">
-        <v>19</v>
-      </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="H66" t="s">
-        <v>22</v>
-      </c>
-      <c r="J66" s="2" t="s">
+      <c r="K66" t="s">
+        <v>18</v>
+      </c>
+      <c r="L66" t="s">
+        <v>18</v>
+      </c>
+      <c r="M66" t="s">
+        <v>18</v>
+      </c>
+      <c r="N66" t="s">
         <v>209</v>
       </c>
-      <c r="K66" t="s">
-        <v>19</v>
-      </c>
-      <c r="L66" t="s">
-        <v>19</v>
-      </c>
-      <c r="M66" t="s">
-        <v>19</v>
-      </c>
-      <c r="N66" t="s">
+      <c r="O66" t="s">
         <v>210</v>
       </c>
-      <c r="O66" t="s">
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="B67" t="s">
         <v>212</v>
       </c>
-      <c r="B67" t="s">
-        <v>213</v>
-      </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D67" t="b">
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G67" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H67" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J67" s="2">
         <v>108</v>
       </c>
       <c r="K67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N67" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="B68" t="s">
         <v>216</v>
       </c>
-      <c r="B68" t="s">
-        <v>217</v>
-      </c>
       <c r="C68" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D68" t="b">
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H68" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N68" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>219</v>
       </c>
-      <c r="B69" t="s">
-        <v>220</v>
-      </c>
       <c r="C69" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D69" t="b">
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J69" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="K69" t="s">
+        <v>19</v>
+      </c>
+      <c r="L69" t="s">
+        <v>18</v>
+      </c>
+      <c r="M69" t="s">
+        <v>18</v>
+      </c>
+      <c r="N69" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>221</v>
       </c>
-      <c r="K69" t="s">
-        <v>20</v>
-      </c>
-      <c r="L69" t="s">
-        <v>19</v>
-      </c>
-      <c r="M69" t="s">
-        <v>19</v>
-      </c>
-      <c r="N69" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="B70" t="s">
         <v>222</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
+        <v>30</v>
+      </c>
+      <c r="D70" t="s">
+        <v>19</v>
+      </c>
+      <c r="E70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K70" t="s">
+        <v>18</v>
+      </c>
+      <c r="L70" t="s">
+        <v>18</v>
+      </c>
+      <c r="M70" t="s">
+        <v>18</v>
+      </c>
+      <c r="N70" t="s">
         <v>223</v>
       </c>
-      <c r="C70" t="s">
-        <v>31</v>
-      </c>
-      <c r="D70" t="s">
-        <v>20</v>
-      </c>
-      <c r="E70" t="s">
-        <v>20</v>
-      </c>
-      <c r="F70" t="s">
-        <v>19</v>
-      </c>
-      <c r="G70" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70" t="s">
-        <v>22</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K70" t="s">
-        <v>19</v>
-      </c>
-      <c r="L70" t="s">
-        <v>19</v>
-      </c>
-      <c r="M70" t="s">
-        <v>19</v>
-      </c>
-      <c r="N70" t="s">
+      <c r="O70" t="s">
         <v>224</v>
       </c>
-      <c r="O70" t="s">
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>226</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
+        <v>30</v>
+      </c>
+      <c r="D71" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K71" t="s">
+        <v>18</v>
+      </c>
+      <c r="L71" t="s">
+        <v>18</v>
+      </c>
+      <c r="M71" t="s">
+        <v>18</v>
+      </c>
+      <c r="N71" t="s">
+        <v>223</v>
+      </c>
+      <c r="O71" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>227</v>
       </c>
-      <c r="C71" t="s">
-        <v>31</v>
-      </c>
-      <c r="D71" t="s">
-        <v>20</v>
-      </c>
-      <c r="E71" t="s">
-        <v>20</v>
-      </c>
-      <c r="F71" t="s">
-        <v>19</v>
-      </c>
-      <c r="G71" t="s">
-        <v>21</v>
-      </c>
-      <c r="H71" t="s">
-        <v>22</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K71" t="s">
-        <v>19</v>
-      </c>
-      <c r="L71" t="s">
-        <v>19</v>
-      </c>
-      <c r="M71" t="s">
-        <v>19</v>
-      </c>
-      <c r="N71" t="s">
+      <c r="B72" t="s">
+        <v>228</v>
+      </c>
+      <c r="C72" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72" t="s">
+        <v>19</v>
+      </c>
+      <c r="E72" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K72" t="s">
+        <v>18</v>
+      </c>
+      <c r="L72" t="s">
+        <v>18</v>
+      </c>
+      <c r="M72" t="s">
+        <v>18</v>
+      </c>
+      <c r="N72" t="s">
+        <v>223</v>
+      </c>
+      <c r="O72" t="s">
         <v>224</v>
       </c>
-      <c r="O71" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>228</v>
-      </c>
-      <c r="B72" t="s">
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>229</v>
       </c>
-      <c r="C72" t="s">
-        <v>31</v>
-      </c>
-      <c r="D72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E72" t="s">
-        <v>20</v>
-      </c>
-      <c r="F72" t="s">
-        <v>19</v>
-      </c>
-      <c r="G72" t="s">
-        <v>21</v>
-      </c>
-      <c r="H72" t="s">
-        <v>22</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K72" t="s">
-        <v>19</v>
-      </c>
-      <c r="L72" t="s">
-        <v>19</v>
-      </c>
-      <c r="M72" t="s">
-        <v>19</v>
-      </c>
-      <c r="N72" t="s">
+      <c r="B73" t="s">
+        <v>230</v>
+      </c>
+      <c r="C73" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" t="s">
+        <v>19</v>
+      </c>
+      <c r="E73" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>20</v>
+      </c>
+      <c r="H73" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K73" t="s">
+        <v>18</v>
+      </c>
+      <c r="L73" t="s">
+        <v>18</v>
+      </c>
+      <c r="M73" t="s">
+        <v>18</v>
+      </c>
+      <c r="N73" t="s">
+        <v>223</v>
+      </c>
+      <c r="O73" t="s">
         <v>224</v>
       </c>
-      <c r="O72" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>230</v>
-      </c>
-      <c r="B73" t="s">
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>231</v>
       </c>
-      <c r="C73" t="s">
-        <v>31</v>
-      </c>
-      <c r="D73" t="s">
-        <v>20</v>
-      </c>
-      <c r="E73" t="s">
-        <v>20</v>
-      </c>
-      <c r="F73" t="s">
-        <v>19</v>
-      </c>
-      <c r="G73" t="s">
-        <v>21</v>
-      </c>
-      <c r="H73" t="s">
-        <v>22</v>
-      </c>
-      <c r="J73" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K73" t="s">
-        <v>19</v>
-      </c>
-      <c r="L73" t="s">
-        <v>19</v>
-      </c>
-      <c r="M73" t="s">
-        <v>19</v>
-      </c>
-      <c r="N73" t="s">
-        <v>224</v>
-      </c>
-      <c r="O73" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
         <v>232</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
+        <v>43</v>
+      </c>
+      <c r="D74" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>20</v>
+      </c>
+      <c r="H74" t="s">
+        <v>21</v>
+      </c>
+      <c r="K74" t="s">
+        <v>18</v>
+      </c>
+      <c r="L74" t="s">
+        <v>18</v>
+      </c>
+      <c r="M74" t="s">
+        <v>18</v>
+      </c>
+      <c r="O74" t="s">
         <v>233</v>
       </c>
-      <c r="C74" t="s">
-        <v>44</v>
-      </c>
-      <c r="D74" t="s">
-        <v>18</v>
-      </c>
-      <c r="E74" t="s">
-        <v>20</v>
-      </c>
-      <c r="F74" t="s">
-        <v>19</v>
-      </c>
-      <c r="G74" t="s">
-        <v>21</v>
-      </c>
-      <c r="H74" t="s">
-        <v>22</v>
-      </c>
-      <c r="K74" t="s">
-        <v>19</v>
-      </c>
-      <c r="L74" t="s">
-        <v>19</v>
-      </c>
-      <c r="M74" t="s">
-        <v>19</v>
-      </c>
-      <c r="O74" t="s">
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="B75" t="s">
         <v>235</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H75" t="s">
+        <v>48</v>
+      </c>
+      <c r="K75" t="s">
+        <v>18</v>
+      </c>
+      <c r="L75" t="s">
+        <v>18</v>
+      </c>
+      <c r="M75" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>236</v>
       </c>
-      <c r="C75" t="s">
-        <v>31</v>
-      </c>
-      <c r="D75" t="s">
-        <v>18</v>
-      </c>
-      <c r="E75" t="s">
-        <v>20</v>
-      </c>
-      <c r="F75" t="s">
-        <v>19</v>
-      </c>
-      <c r="G75" t="s">
-        <v>21</v>
-      </c>
-      <c r="H75" t="s">
-        <v>49</v>
-      </c>
-      <c r="K75" t="s">
-        <v>19</v>
-      </c>
-      <c r="L75" t="s">
-        <v>19</v>
-      </c>
-      <c r="M75" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="B76" t="s">
         <v>237</v>
       </c>
-      <c r="B76" t="s">
-        <v>238</v>
-      </c>
       <c r="C76" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D76" t="b">
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H76" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K76" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L76" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M76" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N76" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>240</v>
       </c>
-      <c r="B77" t="s">
-        <v>241</v>
-      </c>
       <c r="C77" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D77" t="b">
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G77" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H77" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M77" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>241</v>
+      </c>
+      <c r="B78" t="s">
         <v>242</v>
       </c>
-      <c r="B78" t="s">
-        <v>243</v>
-      </c>
       <c r="C78" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D78" t="b">
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G78" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H78" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K78" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L78" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M78" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>243</v>
+      </c>
+      <c r="B79" t="s">
         <v>244</v>
       </c>
-      <c r="B79" t="s">
-        <v>245</v>
-      </c>
       <c r="C79" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D79" t="b">
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H79" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J79" s="2">
         <v>52</v>
       </c>
       <c r="K79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N79" t="s">
+        <v>245</v>
+      </c>
+      <c r="O79" t="s">
         <v>246</v>
       </c>
-      <c r="O79" t="s">
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
         <v>248</v>
       </c>
-      <c r="B80" t="s">
-        <v>249</v>
-      </c>
       <c r="C80" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D80" t="b">
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F80" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G80" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H80" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J80" s="2">
         <v>45</v>
       </c>
       <c r="K80" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L80" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M80" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N80" t="s">
+        <v>245</v>
+      </c>
+      <c r="O80" t="s">
         <v>246</v>
       </c>
-      <c r="O80" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>249</v>
+      </c>
+      <c r="B81" t="s">
         <v>250</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
+        <v>43</v>
+      </c>
+      <c r="D81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C81" t="s">
-        <v>44</v>
-      </c>
-      <c r="D81" t="s">
-        <v>18</v>
-      </c>
-      <c r="E81" t="s">
-        <v>20</v>
-      </c>
-      <c r="F81" t="s">
-        <v>19</v>
-      </c>
-      <c r="G81" t="s">
-        <v>21</v>
-      </c>
-      <c r="H81" t="s">
-        <v>22</v>
-      </c>
-      <c r="J81" s="2" t="s">
+      <c r="K81" t="s">
+        <v>18</v>
+      </c>
+      <c r="L81" t="s">
+        <v>18</v>
+      </c>
+      <c r="M81" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>252</v>
       </c>
-      <c r="K81" t="s">
-        <v>19</v>
-      </c>
-      <c r="L81" t="s">
-        <v>19</v>
-      </c>
-      <c r="M81" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="B82" t="s">
+        <v>195</v>
+      </c>
+      <c r="C82" t="s">
+        <v>43</v>
+      </c>
+      <c r="D82" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>20</v>
+      </c>
+      <c r="H82" t="s">
+        <v>21</v>
+      </c>
+      <c r="J82" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B82" t="s">
-        <v>196</v>
-      </c>
-      <c r="C82" t="s">
-        <v>44</v>
-      </c>
-      <c r="D82" t="s">
-        <v>18</v>
-      </c>
-      <c r="E82" t="s">
-        <v>20</v>
-      </c>
-      <c r="F82" t="s">
-        <v>19</v>
-      </c>
-      <c r="G82" t="s">
-        <v>21</v>
-      </c>
-      <c r="H82" t="s">
-        <v>22</v>
-      </c>
-      <c r="J82" s="2" t="s">
+      <c r="K82" t="s">
+        <v>18</v>
+      </c>
+      <c r="L82" t="s">
+        <v>18</v>
+      </c>
+      <c r="M82" t="s">
+        <v>18</v>
+      </c>
+      <c r="O82" t="s">
         <v>254</v>
       </c>
-      <c r="K82" t="s">
-        <v>19</v>
-      </c>
-      <c r="L82" t="s">
-        <v>19</v>
-      </c>
-      <c r="M82" t="s">
-        <v>19</v>
-      </c>
-      <c r="O82" t="s">
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
         <v>256</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
+        <v>43</v>
+      </c>
+      <c r="D83" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>20</v>
+      </c>
+      <c r="H83" t="s">
+        <v>21</v>
+      </c>
+      <c r="J83" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C83" t="s">
-        <v>44</v>
-      </c>
-      <c r="D83" t="s">
-        <v>18</v>
-      </c>
-      <c r="E83" t="s">
-        <v>20</v>
-      </c>
-      <c r="F83" t="s">
-        <v>19</v>
-      </c>
-      <c r="G83" t="s">
-        <v>21</v>
-      </c>
-      <c r="H83" t="s">
-        <v>22</v>
-      </c>
-      <c r="J83" s="2" t="s">
+      <c r="K83" t="s">
+        <v>18</v>
+      </c>
+      <c r="L83" t="s">
+        <v>18</v>
+      </c>
+      <c r="M83" t="s">
+        <v>18</v>
+      </c>
+      <c r="O83" t="s">
         <v>258</v>
       </c>
-      <c r="K83" t="s">
-        <v>19</v>
-      </c>
-      <c r="L83" t="s">
-        <v>19</v>
-      </c>
-      <c r="M83" t="s">
-        <v>19</v>
-      </c>
-      <c r="O83" t="s">
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
         <v>260</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
+        <v>43</v>
+      </c>
+      <c r="D84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" t="s">
+        <v>21</v>
+      </c>
+      <c r="J84" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C84" t="s">
-        <v>44</v>
-      </c>
-      <c r="D84" t="s">
-        <v>18</v>
-      </c>
-      <c r="E84" t="s">
-        <v>20</v>
-      </c>
-      <c r="F84" t="s">
-        <v>19</v>
-      </c>
-      <c r="G84" t="s">
-        <v>21</v>
-      </c>
-      <c r="H84" t="s">
-        <v>22</v>
-      </c>
-      <c r="J84" s="2" t="s">
+      <c r="K84" t="s">
+        <v>18</v>
+      </c>
+      <c r="L84" t="s">
+        <v>18</v>
+      </c>
+      <c r="M84" t="s">
+        <v>18</v>
+      </c>
+      <c r="N84" t="s">
+        <v>135</v>
+      </c>
+      <c r="O84" t="s">
         <v>262</v>
       </c>
-      <c r="K84" t="s">
-        <v>19</v>
-      </c>
-      <c r="L84" t="s">
-        <v>19</v>
-      </c>
-      <c r="M84" t="s">
-        <v>19</v>
-      </c>
-      <c r="N84" t="s">
-        <v>136</v>
-      </c>
-      <c r="O84" t="s">
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="B85" t="s">
         <v>264</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
+        <v>43</v>
+      </c>
+      <c r="D85" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>20</v>
+      </c>
+      <c r="H85" t="s">
+        <v>21</v>
+      </c>
+      <c r="J85" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C85" t="s">
-        <v>44</v>
-      </c>
-      <c r="D85" t="s">
-        <v>18</v>
-      </c>
-      <c r="E85" t="s">
-        <v>20</v>
-      </c>
-      <c r="F85" t="s">
-        <v>19</v>
-      </c>
-      <c r="G85" t="s">
-        <v>21</v>
-      </c>
-      <c r="H85" t="s">
-        <v>22</v>
-      </c>
-      <c r="J85" s="2" t="s">
+      <c r="K85" t="s">
+        <v>18</v>
+      </c>
+      <c r="L85" t="s">
+        <v>18</v>
+      </c>
+      <c r="M85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>266</v>
       </c>
-      <c r="K85" t="s">
-        <v>19</v>
-      </c>
-      <c r="L85" t="s">
-        <v>19</v>
-      </c>
-      <c r="M85" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="B86" t="s">
         <v>267</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
+        <v>43</v>
+      </c>
+      <c r="D86" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86" t="s">
+        <v>21</v>
+      </c>
+      <c r="J86" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C86" t="s">
-        <v>44</v>
-      </c>
-      <c r="D86" t="s">
-        <v>18</v>
-      </c>
-      <c r="E86" t="s">
-        <v>20</v>
-      </c>
-      <c r="F86" t="s">
-        <v>19</v>
-      </c>
-      <c r="G86" t="s">
-        <v>21</v>
-      </c>
-      <c r="H86" t="s">
-        <v>22</v>
-      </c>
-      <c r="J86" s="2" t="s">
+      <c r="K86" t="s">
+        <v>18</v>
+      </c>
+      <c r="L86" t="s">
+        <v>18</v>
+      </c>
+      <c r="M86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>269</v>
       </c>
-      <c r="K86" t="s">
-        <v>19</v>
-      </c>
-      <c r="L86" t="s">
-        <v>19</v>
-      </c>
-      <c r="M86" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="B87" t="s">
         <v>270</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
+        <v>43</v>
+      </c>
+      <c r="D87" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>20</v>
+      </c>
+      <c r="H87" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K87" t="s">
+        <v>18</v>
+      </c>
+      <c r="L87" t="s">
+        <v>18</v>
+      </c>
+      <c r="M87" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>271</v>
       </c>
-      <c r="C87" t="s">
-        <v>44</v>
-      </c>
-      <c r="D87" t="s">
-        <v>18</v>
-      </c>
-      <c r="E87" t="s">
-        <v>20</v>
-      </c>
-      <c r="F87" t="s">
-        <v>19</v>
-      </c>
-      <c r="G87" t="s">
-        <v>21</v>
-      </c>
-      <c r="H87" t="s">
-        <v>22</v>
-      </c>
-      <c r="J87" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="K87" t="s">
-        <v>19</v>
-      </c>
-      <c r="L87" t="s">
-        <v>19</v>
-      </c>
-      <c r="M87" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="B88" t="s">
         <v>272</v>
       </c>
-      <c r="B88" t="s">
-        <v>273</v>
-      </c>
       <c r="C88" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D88" t="b">
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F88" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G88" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H88" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K88" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L88" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M88" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N88" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="B89" t="s">
         <v>275</v>
       </c>
-      <c r="B89" t="s">
-        <v>276</v>
-      </c>
       <c r="C89" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D89" t="b">
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G89" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H89" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L89" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M89" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N89" t="s">
+        <v>276</v>
+      </c>
+      <c r="O89" t="s">
         <v>277</v>
       </c>
-      <c r="O89" t="s">
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="B90" t="s">
         <v>279</v>
       </c>
-      <c r="B90" t="s">
-        <v>280</v>
-      </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D90" t="b">
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H90" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N90" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="B91" t="s">
         <v>282</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
+        <v>43</v>
+      </c>
+      <c r="D91" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" t="s">
+        <v>19</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C91" t="s">
-        <v>44</v>
-      </c>
-      <c r="D91" t="s">
-        <v>18</v>
-      </c>
-      <c r="E91" t="s">
-        <v>20</v>
-      </c>
-      <c r="F91" t="s">
-        <v>19</v>
-      </c>
-      <c r="G91" t="s">
-        <v>21</v>
-      </c>
-      <c r="H91" t="s">
-        <v>22</v>
-      </c>
-      <c r="J91" s="2" t="s">
+      <c r="K91" t="s">
+        <v>18</v>
+      </c>
+      <c r="L91" t="s">
+        <v>18</v>
+      </c>
+      <c r="M91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>284</v>
       </c>
-      <c r="K91" t="s">
-        <v>19</v>
-      </c>
-      <c r="L91" t="s">
-        <v>19</v>
-      </c>
-      <c r="M91" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="B92" t="s">
         <v>285</v>
       </c>
-      <c r="B92" t="s">
-        <v>286</v>
-      </c>
       <c r="C92" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D92" t="b">
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G92" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H92" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M92" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>286</v>
+      </c>
+      <c r="B93" t="s">
         <v>287</v>
       </c>
-      <c r="B93" t="s">
-        <v>288</v>
-      </c>
       <c r="C93" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D93" t="b">
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G93" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H93" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K93" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L93" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M93" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>288</v>
+      </c>
+      <c r="B94" t="s">
         <v>289</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
+        <v>43</v>
+      </c>
+      <c r="D94" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" t="s">
+        <v>18</v>
+      </c>
+      <c r="F94" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" t="s">
+        <v>20</v>
+      </c>
+      <c r="H94" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="K94" t="s">
+        <v>18</v>
+      </c>
+      <c r="L94" t="s">
+        <v>18</v>
+      </c>
+      <c r="M94" t="s">
+        <v>18</v>
+      </c>
+      <c r="O94" t="s">
         <v>290</v>
       </c>
-      <c r="C94" t="s">
-        <v>44</v>
-      </c>
-      <c r="D94" t="s">
-        <v>20</v>
-      </c>
-      <c r="E94" t="s">
-        <v>19</v>
-      </c>
-      <c r="F94" t="s">
-        <v>19</v>
-      </c>
-      <c r="G94" t="s">
-        <v>21</v>
-      </c>
-      <c r="H94" t="s">
-        <v>22</v>
-      </c>
-      <c r="J94" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="K94" t="s">
-        <v>19</v>
-      </c>
-      <c r="L94" t="s">
-        <v>19</v>
-      </c>
-      <c r="M94" t="s">
-        <v>19</v>
-      </c>
-      <c r="O94" t="s">
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+      <c r="B95" t="s">
         <v>292</v>
       </c>
-      <c r="B95" t="s">
-        <v>293</v>
-      </c>
       <c r="C95" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D95" t="b">
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G95" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H95" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K95" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L95" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M95" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>293</v>
+      </c>
+      <c r="B96" t="s">
         <v>294</v>
       </c>
-      <c r="B96" t="s">
-        <v>295</v>
-      </c>
       <c r="C96" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D96" t="b">
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G96" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H96" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K96" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N96" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O96" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+      <c r="B97" t="s">
         <v>297</v>
       </c>
-      <c r="B97" t="s">
-        <v>298</v>
-      </c>
       <c r="C97" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D97" t="b">
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F97" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H97" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K97" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L97" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M97" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>298</v>
+      </c>
+      <c r="B98" t="s">
         <v>299</v>
       </c>
-      <c r="B98" t="s">
-        <v>300</v>
-      </c>
       <c r="C98" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D98" t="b">
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F98" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G98" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H98" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K98" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L98" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M98" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>300</v>
+      </c>
+      <c r="B99" t="s">
         <v>301</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
+        <v>43</v>
+      </c>
+      <c r="D99" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" t="s">
+        <v>20</v>
+      </c>
+      <c r="H99" t="s">
+        <v>21</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K99" t="s">
+        <v>18</v>
+      </c>
+      <c r="L99" t="s">
+        <v>18</v>
+      </c>
+      <c r="M99" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>302</v>
       </c>
-      <c r="C99" t="s">
-        <v>44</v>
-      </c>
-      <c r="D99" t="s">
-        <v>18</v>
-      </c>
-      <c r="E99" t="s">
-        <v>20</v>
-      </c>
-      <c r="F99" t="s">
-        <v>19</v>
-      </c>
-      <c r="G99" t="s">
-        <v>21</v>
-      </c>
-      <c r="H99" t="s">
-        <v>22</v>
-      </c>
-      <c r="J99" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="K99" t="s">
-        <v>19</v>
-      </c>
-      <c r="L99" t="s">
-        <v>19</v>
-      </c>
-      <c r="M99" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="B100" t="s">
         <v>303</v>
       </c>
-      <c r="B100" t="s">
-        <v>304</v>
-      </c>
       <c r="C100" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D100" t="b">
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F100" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G100" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H100" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K100" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L100" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M100" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N100" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="B101" t="s">
         <v>306</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
+        <v>43</v>
+      </c>
+      <c r="D101" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" t="s">
+        <v>18</v>
+      </c>
+      <c r="F101" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" t="s">
+        <v>20</v>
+      </c>
+      <c r="H101" t="s">
+        <v>21</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="K101" t="s">
+        <v>18</v>
+      </c>
+      <c r="L101" t="s">
+        <v>18</v>
+      </c>
+      <c r="M101" t="s">
+        <v>18</v>
+      </c>
+      <c r="O101" t="s">
         <v>307</v>
       </c>
-      <c r="C101" t="s">
-        <v>44</v>
-      </c>
-      <c r="D101" t="s">
-        <v>20</v>
-      </c>
-      <c r="E101" t="s">
-        <v>19</v>
-      </c>
-      <c r="F101" t="s">
-        <v>19</v>
-      </c>
-      <c r="G101" t="s">
-        <v>21</v>
-      </c>
-      <c r="H101" t="s">
-        <v>22</v>
-      </c>
-      <c r="J101" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="K101" t="s">
-        <v>19</v>
-      </c>
-      <c r="L101" t="s">
-        <v>19</v>
-      </c>
-      <c r="M101" t="s">
-        <v>19</v>
-      </c>
-      <c r="O101" t="s">
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="B102" t="s">
         <v>309</v>
       </c>
-      <c r="B102" t="s">
-        <v>310</v>
-      </c>
       <c r="C102" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D102" t="b">
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F102" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G102" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H102" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J102" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="K102" t="s">
+        <v>18</v>
+      </c>
+      <c r="L102" t="s">
+        <v>18</v>
+      </c>
+      <c r="M102" t="s">
+        <v>18</v>
+      </c>
+      <c r="N102" t="s">
         <v>311</v>
       </c>
-      <c r="K102" t="s">
-        <v>19</v>
-      </c>
-      <c r="L102" t="s">
-        <v>19</v>
-      </c>
-      <c r="M102" t="s">
-        <v>19</v>
-      </c>
-      <c r="N102" t="s">
+      <c r="O102" t="s">
         <v>312</v>
       </c>
-      <c r="O102" t="s">
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="B103" t="s">
         <v>314</v>
       </c>
-      <c r="B103" t="s">
-        <v>315</v>
-      </c>
       <c r="C103" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D103" t="b">
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F103" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G103" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H103" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K103" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L103" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M103" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>315</v>
+      </c>
+      <c r="B104" t="s">
         <v>316</v>
       </c>
-      <c r="B104" t="s">
-        <v>317</v>
-      </c>
       <c r="C104" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D104" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E104" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F104" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G104" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H104" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J104" s="2">
         <v>127</v>
       </c>
       <c r="K104" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L104" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M104" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>317</v>
+      </c>
+      <c r="B105" t="s">
         <v>318</v>
       </c>
-      <c r="B105" t="s">
-        <v>319</v>
-      </c>
       <c r="C105" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D105" t="b">
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F105" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G105" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H105" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J105" s="2">
         <v>159</v>
       </c>
       <c r="K105" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L105" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M105" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N105" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="B106" t="s">
         <v>321</v>
       </c>
-      <c r="B106" t="s">
-        <v>322</v>
-      </c>
       <c r="C106" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D106" t="b">
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F106" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H106" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J106" s="2">
         <v>159</v>
       </c>
       <c r="K106" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L106" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M106" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N106" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="B107" t="s">
         <v>324</v>
       </c>
-      <c r="B107" t="s">
-        <v>325</v>
-      </c>
       <c r="C107" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D107" t="b">
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F107" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G107" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H107" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J107" s="2">
         <v>159</v>
       </c>
       <c r="K107" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M107" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N107" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>325</v>
+      </c>
+      <c r="B108" t="s">
         <v>326</v>
       </c>
-      <c r="B108" t="s">
-        <v>327</v>
-      </c>
       <c r="C108" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D108" t="b">
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F108" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G108" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H108" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J108" s="2">
         <v>159</v>
       </c>
       <c r="K108" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L108" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M108" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N108" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>327</v>
+      </c>
+      <c r="B109" t="s">
         <v>328</v>
       </c>
-      <c r="B109" t="s">
-        <v>329</v>
-      </c>
       <c r="C109" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D109" t="b">
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F109" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G109" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H109" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J109" s="2">
         <v>159</v>
       </c>
       <c r="K109" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L109" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M109" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N109" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>330</v>
+      </c>
+      <c r="B110" t="s">
         <v>331</v>
       </c>
-      <c r="B110" t="s">
-        <v>332</v>
-      </c>
       <c r="C110" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D110" t="b">
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F110" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G110" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H110" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J110" s="2">
         <v>159</v>
       </c>
       <c r="K110" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L110" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M110" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N110" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>332</v>
+      </c>
+      <c r="B111" t="s">
         <v>333</v>
       </c>
-      <c r="B111" t="s">
-        <v>334</v>
-      </c>
       <c r="C111" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D111" t="b">
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F111" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G111" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H111" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J111" s="2">
         <v>108</v>
       </c>
       <c r="K111" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L111" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M111" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N111" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>334</v>
+      </c>
+      <c r="B112" t="s">
         <v>335</v>
       </c>
-      <c r="B112" t="s">
-        <v>336</v>
-      </c>
       <c r="C112" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D112" t="b">
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F112" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G112" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H112" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J112" s="2">
         <v>111</v>
       </c>
       <c r="K112" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L112" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M112" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N112" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+      <c r="B113" t="s">
         <v>338</v>
       </c>
-      <c r="B113" t="s">
-        <v>339</v>
-      </c>
       <c r="C113" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D113" t="b">
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F113" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G113" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H113" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K113" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L113" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M113" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N113" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>339</v>
+      </c>
+      <c r="B114" t="s">
         <v>340</v>
       </c>
-      <c r="B114" t="s">
-        <v>341</v>
-      </c>
       <c r="C114" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D114" t="b">
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F114" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G114" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H114" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K114" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L114" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M114" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N114" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>341</v>
+      </c>
+      <c r="B115" t="s">
         <v>342</v>
       </c>
-      <c r="B115" t="s">
+      <c r="K115" t="s">
+        <v>18</v>
+      </c>
+      <c r="L115" t="s">
+        <v>18</v>
+      </c>
+      <c r="M115" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>341</v>
+      </c>
+      <c r="B116" t="s">
         <v>343</v>
       </c>
-      <c r="K115" t="s">
-        <v>19</v>
-      </c>
-      <c r="L115" t="s">
-        <v>19</v>
-      </c>
-      <c r="M115" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>342</v>
-      </c>
-      <c r="B116" t="s">
-        <v>344</v>
-      </c>
       <c r="C116" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D116" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E116" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F116" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G116" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H116" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K116" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L116" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M116" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
